--- a/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
+++ b/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\nas01.itap.purdue.edu\puhome\desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF320C90-E5DA-41F4-93D7-1188D7FEA2C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4447D4-8053-4676-AC00-7E68C4D6F1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10678,11 +10678,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'894'!$C$3</c:f>
+              <c:f>'894'!$G$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jun09,2026</c:v>
+                  <c:v>Jun15,2030</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10830,69 +10830,102 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'894'!$C$4:$C$233</c:f>
+              <c:f>'894'!$G$4:$G$233</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="230"/>
                 <c:pt idx="0">
-                  <c:v>8.53551089338964</c:v>
+                  <c:v>15.5831740366148</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.2121360213246692</c:v>
+                  <c:v>15.6181213588261</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.3727208112640206</c:v>
+                  <c:v>15.471660411280601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.4364141305933895</c:v>
+                  <c:v>15.4286358328345</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.4084015562695207</c:v>
+                  <c:v>15.725390191826</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.5099572412062301</c:v>
+                  <c:v>15.6295450777592</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.4321434520724008</c:v>
+                  <c:v>15.5447105698267</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.4721216638779193</c:v>
+                  <c:v>15.641779033917301</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.4953666075608503</c:v>
+                  <c:v>15.560241393406899</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.7711252103094601</c:v>
+                  <c:v>15.6798903930978</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.5801266895029205</c:v>
+                  <c:v>15.5257705053734</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8.5783681642005494</c:v>
+                  <c:v>15.5068553708303</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.6129268121772302</c:v>
+                  <c:v>15.7245514226287</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.6349505815443095</c:v>
+                  <c:v>15.653971830187899</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.5827352500219707</c:v>
+                  <c:v>15.585241971938</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.6784045244654298</c:v>
+                  <c:v>15.591441713773801</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8.5889121451567796</c:v>
+                  <c:v>15.513624662526899</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.2237273067390202</c:v>
+                  <c:v>15.550450799138201</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.26640584418465</c:v>
+                  <c:v>15.5999990421973</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.2614937671479094</c:v>
+                  <c:v>15.5612294230614</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>15.389959627991299</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>15.6769168147221</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>15.516217850365001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15.4712021433598</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>15.4267437621642</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15.363023447442201</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.4784018893041</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>15.598700910453401</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.699463941581101</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15.751226314712399</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>15.601321813860199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14987,16 +15020,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>171449</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>233632</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>107830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>560359</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>512191</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15025,14 +15058,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>476250</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15213,16 +15246,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -19196,7 +19229,7 @@
         <v>0.82580237252011701</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:K2" si="1">100*C1/AVERAGE(C4:C39)</f>
+        <f t="shared" ref="C2:J2" si="1">100*C1/AVERAGE(C4:C39)</f>
         <v>0.41179120150630028</v>
       </c>
       <c r="D2">

--- a/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
+++ b/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4447D4-8053-4676-AC00-7E68C4D6F1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5562D9B-800E-4A8B-A55A-17EAFFE389C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Together" sheetId="1" r:id="rId1"/>
@@ -30,9 +30,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2662,6 +2659,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2669,7 +2667,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4661,6 +4658,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4668,7 +4666,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4953,6 +4950,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4960,7 +4958,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7533,6 +7530,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7540,7 +7538,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8001,6 +7998,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8008,7 +8006,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10581,6 +10578,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10588,7 +10586,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11082,6 +11079,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11089,7 +11087,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15020,16 +15017,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>233632</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>107830</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>491226</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>527170</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>560359</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>512191</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>117056</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>380399</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15546,13 +15543,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P233"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P295"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15593,7 +15590,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15647,7 +15644,7 @@
         <v>5.1155359965755959E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -15701,7 +15698,7 @@
         <v>1.2279085192200808E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -15715,7 +15712,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -15726,7 +15723,7 @@
         <v>0.17477778117201601</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -15737,7 +15734,7 @@
         <v>0.17496986858800301</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -15748,7 +15745,7 @@
         <v>0.39075425090921301</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -15759,7 +15756,7 @@
         <v>0.39090251610402299</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -15770,7 +15767,7 @@
         <v>0.38163793874347302</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -15781,7 +15778,7 @@
         <v>0.38646897393750201</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -15792,7 +15789,7 @@
         <v>0.38820632020412599</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -15803,7 +15800,7 @@
         <v>0.391100077546855</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -15814,7 +15811,7 @@
         <v>0.37812534333091802</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -15825,7 +15822,7 @@
         <v>0.38449528426413199</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -15836,7 +15833,7 @@
         <v>0.38779470041263903</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -15847,7 +15844,7 @@
         <v>0.378248054436716</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -15858,7 +15855,7 @@
         <v>0.388322173460803</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -15869,7 +15866,7 @@
         <v>0.38881861759339797</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -15880,7 +15877,7 @@
         <v>0.39254780032303299</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -15891,7 +15888,7 @@
         <v>0.38860291038577099</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -15902,7 +15899,7 @@
         <v>0.391344107724999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -15913,7 +15910,7 @@
         <v>0.39401793952400199</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -15924,7 +15921,7 @@
         <v>0.398157579716993</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -15935,7 +15932,7 @@
         <v>0.38710256673105198</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -15946,7 +15943,7 @@
         <v>0.18265936593662399</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -15957,7 +15954,7 @@
         <v>0.17720413354468001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -15968,7 +15965,7 @@
         <v>0.183642067498062</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -15979,7 +15976,7 @@
         <v>0.18126642652018499</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -15990,7 +15987,7 @@
         <v>0.17863631678412401</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -16001,7 +15998,7 @@
         <v>0.18200369359492499</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -16012,7 +16009,7 @@
         <v>0.18140063454570701</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -16023,7 +16020,7 @@
         <v>0.14198189433295499</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -16034,7 +16031,7 @@
         <v>0.14200693706074399</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -16045,7 +16042,7 @@
         <v>0.13879302222888601</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -16056,7 +16053,7 @@
         <v>0.14134057599559999</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -16067,7 +16064,7 @@
         <v>0.14287369952523299</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -16078,7 +16075,7 @@
         <v>0.14242039757473199</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -16089,7 +16086,7 @@
         <v>0.13513280226965799</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -16100,7 +16097,7 @@
         <v>0.13504563445130599</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -16111,7 +16108,7 @@
         <v>0.13859780418944301</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -16122,7 +16119,7 @@
         <v>0.13768382280778599</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -16133,7 +16130,7 @@
         <v>0.137341027012235</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -16144,7 +16141,7 @@
         <v>0.14146322755453</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -16155,7 +16152,7 @@
         <v>0.1440878295095</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -16166,7 +16163,7 @@
         <v>0.139203017324112</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -16177,7 +16174,7 @@
         <v>0.14444988833485001</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -16188,7 +16185,7 @@
         <v>0.14486186097849299</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -16199,7 +16196,7 @@
         <v>0.14493175120103199</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
@@ -16210,7 +16207,7 @@
         <v>0.14335784354365599</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -16221,7 +16218,7 @@
         <v>0.14372426788936199</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -16232,7 +16229,7 @@
         <v>0.140914458888726</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -16243,7 +16240,7 @@
         <v>0.144559929539015</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -16254,7 +16251,7 @@
         <v>0.13911305366694399</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
@@ -16265,7 +16262,7 @@
         <v>0.136881983671574</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -16276,7 +16273,7 @@
         <v>0.135891683439223</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -16287,7 +16284,7 @@
         <v>0.134600217130598</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
@@ -16298,7 +16295,7 @@
         <v>0.117218052017694</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -16309,7 +16306,7 @@
         <v>0.116738218899043</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
@@ -16320,7 +16317,7 @@
         <v>0.116641895814922</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -16331,7 +16328,7 @@
         <v>0.117986722306339</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -16342,7 +16339,7 @@
         <v>0.116363944216263</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
@@ -16353,7 +16350,7 @@
         <v>0.117960737624138</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -16364,7 +16361,7 @@
         <v>0.11777189549636199</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -16375,7 +16372,7 @@
         <v>0.118362346500101</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -16386,7 +16383,7 @@
         <v>0.11875028071223</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
@@ -16397,7 +16394,7 @@
         <v>0.118209453954305</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
@@ -16408,7 +16405,7 @@
         <v>0.116577694816434</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -16419,7 +16416,7 @@
         <v>0.117670638852321</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
@@ -16430,7 +16427,7 @@
         <v>0.118098845799444</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -16441,7 +16438,7 @@
         <v>0.11655919684067299</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
@@ -16452,7 +16449,7 @@
         <v>0.118487075826876</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
@@ -16463,7 +16460,7 @@
         <v>0.117049111989703</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
@@ -16474,7 +16471,7 @@
         <v>0.116964493443121</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -16485,7 +16482,7 @@
         <v>0.1174932059815</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
@@ -16496,7 +16493,7 @@
         <v>0.118724780988732</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
@@ -16507,7 +16504,7 @@
         <v>0.11857414162119</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
@@ -16518,7 +16515,7 @@
         <v>0.116857985488521</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
@@ -16529,7 +16526,7 @@
         <v>0.117839930521939</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
@@ -16540,7 +16537,7 @@
         <v>0.116123290748398</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
@@ -16551,7 +16548,7 @@
         <v>0.116339626646247</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
@@ -16562,7 +16559,7 @@
         <v>0.118521454357363</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -16573,7 +16570,7 @@
         <v>0.117743388207075</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -16584,7 +16581,7 @@
         <v>0.116823099810358</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
@@ -16595,7 +16592,7 @@
         <v>0.118509294607666</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
@@ -16606,7 +16603,7 @@
         <v>0.118631007440724</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
@@ -16617,7 +16614,7 @@
         <v>0.117484320873481</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -16628,7 +16625,7 @@
         <v>0.118251546607688</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -16639,7 +16636,7 @@
         <v>0.118181098472526</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
@@ -16650,7 +16647,7 @@
         <v>8.9287039240001795E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -16661,7 +16658,7 @@
         <v>8.9953273584561996E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
@@ -16672,7 +16669,7 @@
         <v>9.1230909809772498E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -16683,7 +16680,7 @@
         <v>9.0037965159722497E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -16694,7 +16691,7 @@
         <v>9.2063662732121604E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
@@ -16705,7 +16702,7 @@
         <v>9.0566169869859395E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
@@ -16716,7 +16713,7 @@
         <v>9.1281359996997199E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
@@ -16727,7 +16724,7 @@
         <v>9.0246189977935598E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
@@ -16738,7 +16735,7 @@
         <v>8.7987770056780296E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
@@ -16749,7 +16746,7 @@
         <v>9.1038024594974204E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
@@ -16760,7 +16757,7 @@
         <v>9.0356969610468907E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -16771,7 +16768,7 @@
         <v>8.9055177802521202E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
@@ -16782,7 +16779,7 @@
         <v>9.0556231765949805E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -16793,7 +16790,7 @@
         <v>9.1259865204828206E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
@@ -16804,7 +16801,7 @@
         <v>8.8371089308141498E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
@@ -16815,7 +16812,7 @@
         <v>8.9886315679026302E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -16826,7 +16823,7 @@
         <v>0.22378459935658199</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
@@ -16837,7 +16834,7 @@
         <v>0.228434718604688</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
@@ -16848,7 +16845,7 @@
         <v>0.221372998488612</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
@@ -16859,7 +16856,7 @@
         <v>0.225975457594905</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
@@ -16870,7 +16867,7 @@
         <v>0.225216837741747</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
@@ -16881,7 +16878,7 @@
         <v>0.229746279532067</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
@@ -16892,7 +16889,7 @@
         <v>0.22722518963626401</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
@@ -16903,7 +16900,7 @@
         <v>0.222965184868961</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
@@ -16914,7 +16911,7 @@
         <v>0.22898718060617901</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
@@ -16925,7 +16922,7 @@
         <v>0.22580668748875701</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>116</v>
       </c>
@@ -16936,7 +16933,7 @@
         <v>0.231594890582631</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
@@ -16947,7 +16944,7 @@
         <v>0.224583618990919</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
@@ -16958,7 +16955,7 @@
         <v>0.23249128317182099</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
@@ -16969,7 +16966,7 @@
         <v>0.23073510515949899</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
@@ -16980,7 +16977,7 @@
         <v>0.229179326874075</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>121</v>
       </c>
@@ -16991,7 +16988,7 @@
         <v>0.226024665246639</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>122</v>
       </c>
@@ -17002,7 +16999,7 @@
         <v>0.22988414195496401</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>123</v>
       </c>
@@ -17013,7 +17010,7 @@
         <v>0.22795719930278499</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
@@ -17024,7 +17021,7 @@
         <v>0.227267035209756</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>125</v>
       </c>
@@ -17035,7 +17032,7 @@
         <v>0.22728875634974799</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>126</v>
       </c>
@@ -17046,7 +17043,7 @@
         <v>0.22819660608103401</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>127</v>
       </c>
@@ -17057,7 +17054,7 @@
         <v>0.22449918198189101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>128</v>
       </c>
@@ -17068,7 +17065,7 @@
         <v>0.22352994908158599</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
@@ -17079,7 +17076,7 @@
         <v>0.22753327784977401</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
@@ -17090,7 +17087,7 @@
         <v>0.22784419865740199</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
@@ -17101,7 +17098,7 @@
         <v>0.225433003733543</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
@@ -17112,7 +17109,7 @@
         <v>0.22712348211729699</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
@@ -17123,7 +17120,7 @@
         <v>0.22894109101944199</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
@@ -17134,7 +17131,7 @@
         <v>0.23027592968354901</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
@@ -17145,7 +17142,7 @@
         <v>0.22733899516780401</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
@@ -17156,7 +17153,7 @@
         <v>0.22718964047891599</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
@@ -17167,7 +17164,7 @@
         <v>0.22249606599096799</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
@@ -17178,7 +17175,7 @@
         <v>0.22770140189949001</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
@@ -17189,7 +17186,7 @@
         <v>0.22467693879523801</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
@@ -17200,7 +17197,7 @@
         <v>0.22590951148508701</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
@@ -17211,7 +17208,7 @@
         <v>0.22795873224990801</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
@@ -17222,7 +17219,7 @@
         <v>0.26064960163891099</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
@@ -17233,7 +17230,7 @@
         <v>0.25338188968269398</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
@@ -17244,7 +17241,7 @@
         <v>0.25038094455952498</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
@@ -17255,7 +17252,7 @@
         <v>0.256215228918099</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
@@ -17266,7 +17263,7 @@
         <v>0.25483329669185101</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
@@ -17277,7 +17274,7 @@
         <v>0.25854387484878599</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
@@ -17288,7 +17285,7 @@
         <v>0.25519336396030601</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -17299,7 +17296,7 @@
         <v>0.25663303680948102</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
@@ -17310,7 +17307,7 @@
         <v>0.25601459599486398</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
@@ -17321,7 +17318,7 @@
         <v>0.25648553124648299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
@@ -17332,7 +17329,7 @@
         <v>0.25339182435774998</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
@@ -17343,7 +17340,7 @@
         <v>0.26261256236820102</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
@@ -17354,7 +17351,7 @@
         <v>0.25914013258546797</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
@@ -17365,7 +17362,7 @@
         <v>0.25187380012057398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
@@ -17376,7 +17373,7 @@
         <v>0.25861462842520899</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
@@ -17387,7 +17384,7 @@
         <v>0.26412000142144099</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
@@ -17398,7 +17395,7 @@
         <v>0.25505739125523702</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
@@ -17409,7 +17406,7 @@
         <v>0.25268334549192301</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
@@ -17420,7 +17417,7 @@
         <v>0.254203134019032</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
@@ -17431,7 +17428,7 @@
         <v>0.25355249186689299</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
@@ -17442,7 +17439,7 @@
         <v>0.258640908855092</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
@@ -17453,7 +17450,7 @@
         <v>0.25176887581155899</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
@@ -17464,7 +17461,7 @@
         <v>0.25436276153236997</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
@@ -17475,7 +17472,7 @@
         <v>0.25848980394328103</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
@@ -17486,7 +17483,7 @@
         <v>0.25493042534243598</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
@@ -17497,7 +17494,7 @@
         <v>0.25702073078272197</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
@@ -17508,7 +17505,7 @@
         <v>0.25281370286486299</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
@@ -17519,7 +17516,7 @@
         <v>0.25787828139437702</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
@@ -17530,7 +17527,7 @@
         <v>0.255030114263046</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
@@ -17541,7 +17538,7 @@
         <v>0.25326708245889501</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -17552,7 +17549,7 @@
         <v>0.25901851572451601</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>173</v>
       </c>
@@ -17563,7 +17560,7 @@
         <v>0.25402214979933802</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>174</v>
       </c>
@@ -17574,7 +17571,7 @@
         <v>0.25207440807669201</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>175</v>
       </c>
@@ -17585,7 +17582,7 @@
         <v>0.25648835225167999</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
@@ -17596,7 +17593,7 @@
         <v>0.25619702232418301</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>177</v>
       </c>
@@ -17607,7 +17604,7 @@
         <v>0.256904989972564</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>178</v>
       </c>
@@ -17618,7 +17615,7 @@
         <v>0.25656545981822299</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>179</v>
       </c>
@@ -17629,7 +17626,7 @@
         <v>0.25471437628790899</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>180</v>
       </c>
@@ -17640,7 +17637,7 @@
         <v>0.25564492601438199</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>181</v>
       </c>
@@ -17651,7 +17648,7 @@
         <v>0.26266359379455601</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>182</v>
       </c>
@@ -17662,7 +17659,7 @@
         <v>0.25914186884267898</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>183</v>
       </c>
@@ -17673,7 +17670,7 @@
         <v>0.25621155685651098</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>184</v>
       </c>
@@ -17684,7 +17681,7 @@
         <v>0.25866494788723898</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>185</v>
       </c>
@@ -17695,7 +17692,7 @@
         <v>0.25801756322347102</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>186</v>
       </c>
@@ -17706,7 +17703,7 @@
         <v>0.25944545650678502</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>187</v>
       </c>
@@ -17717,7 +17714,7 @@
         <v>0.25336488450504602</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>188</v>
       </c>
@@ -17728,7 +17725,7 @@
         <v>0.261553420142073</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>189</v>
       </c>
@@ -17739,7 +17736,7 @@
         <v>0.26019522603942802</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>190</v>
       </c>
@@ -17750,7 +17747,7 @@
         <v>0.25868729407005198</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>191</v>
       </c>
@@ -17761,7 +17758,7 @@
         <v>0.25516460879894798</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
@@ -17772,7 +17769,7 @@
         <v>0.25295075090609098</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>193</v>
       </c>
@@ -17783,7 +17780,7 @@
         <v>0.256452611497334</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>194</v>
       </c>
@@ -17794,7 +17791,7 @@
         <v>0.25868777299010298</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
@@ -17805,7 +17802,7 @@
         <v>0.2539674766801</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
@@ -17816,7 +17813,7 @@
         <v>0.17294771128421699</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>197</v>
       </c>
@@ -17827,7 +17824,7 @@
         <v>0.175665485735155</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>198</v>
       </c>
@@ -17838,7 +17835,7 @@
         <v>0.17382778027635701</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>199</v>
       </c>
@@ -17849,7 +17846,7 @@
         <v>0.17455983570099701</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>200</v>
       </c>
@@ -17860,7 +17857,7 @@
         <v>0.17664296551393399</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>201</v>
       </c>
@@ -17871,7 +17868,7 @@
         <v>0.17708531560420199</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>202</v>
       </c>
@@ -17882,7 +17879,7 @@
         <v>0.17557573140333699</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>203</v>
       </c>
@@ -17893,7 +17890,7 @@
         <v>0.173457649972002</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>204</v>
       </c>
@@ -17904,7 +17901,7 @@
         <v>0.17535865105134299</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>205</v>
       </c>
@@ -17915,7 +17912,7 @@
         <v>0.175039518424147</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>206</v>
       </c>
@@ -17926,7 +17923,7 @@
         <v>0.17459939950666101</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>207</v>
       </c>
@@ -17937,7 +17934,7 @@
         <v>0.17177387798819599</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>208</v>
       </c>
@@ -17948,7 +17945,7 @@
         <v>0.172049396498035</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>209</v>
       </c>
@@ -17959,7 +17956,7 @@
         <v>0.17416028353340501</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>210</v>
       </c>
@@ -17970,7 +17967,7 @@
         <v>0.17432866559164001</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>211</v>
       </c>
@@ -17981,7 +17978,7 @@
         <v>0.17371638201273101</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>212</v>
       </c>
@@ -17992,7 +17989,7 @@
         <v>0.17123203171632401</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>213</v>
       </c>
@@ -18003,7 +18000,7 @@
         <v>0.17318569822136001</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>214</v>
       </c>
@@ -18014,7 +18011,7 @@
         <v>0.17669669700448201</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>215</v>
       </c>
@@ -18025,7 +18022,7 @@
         <v>0.17723933870696301</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>216</v>
       </c>
@@ -18036,7 +18033,7 @@
         <v>0.17063092731327101</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>217</v>
       </c>
@@ -18047,7 +18044,7 @@
         <v>0.17490193092626999</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>218</v>
       </c>
@@ -18058,7 +18055,7 @@
         <v>0.17702310390171999</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>219</v>
       </c>
@@ -18069,7 +18066,7 @@
         <v>0.171948853936535</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>220</v>
       </c>
@@ -18080,7 +18077,7 @@
         <v>0.17411860264206899</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>221</v>
       </c>
@@ -18091,7 +18088,7 @@
         <v>0.175935205113702</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>222</v>
       </c>
@@ -18102,7 +18099,7 @@
         <v>0.17427622300988699</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>223</v>
       </c>
@@ -18113,7 +18110,7 @@
         <v>0.17224969239811899</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>224</v>
       </c>
@@ -18124,7 +18121,7 @@
         <v>0.17435257559575301</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>225</v>
       </c>
@@ -18135,7 +18132,7 @@
         <v>0.171222354567128</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>226</v>
       </c>
@@ -18146,7 +18143,7 @@
         <v>0.17230494746765301</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>227</v>
       </c>
@@ -18157,7 +18154,7 @@
         <v>0.17976030708667101</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>228</v>
       </c>
@@ -18168,7 +18165,7 @@
         <v>0.174433801903358</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>229</v>
       </c>
@@ -18179,7 +18176,7 @@
         <v>0.17714435708530099</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>230</v>
       </c>
@@ -18190,7 +18187,7 @@
         <v>0.17086804073973499</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>231</v>
       </c>
@@ -18201,7 +18198,7 @@
         <v>0.171697248433512</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>232</v>
       </c>
@@ -18212,7 +18209,7 @@
         <v>0.17443666559002999</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>233</v>
       </c>
@@ -18223,7 +18220,7 @@
         <v>0.17690051952166999</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>234</v>
       </c>
@@ -18233,6 +18230,254 @@
       <c r="C233" s="1">
         <v>0.17654554655181801</v>
       </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+    </row>
+    <row r="257" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+    </row>
+    <row r="258" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+    </row>
+    <row r="259" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+    </row>
+    <row r="260" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+    </row>
+    <row r="261" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+    </row>
+    <row r="262" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+    </row>
+    <row r="263" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+    </row>
+    <row r="264" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+    </row>
+    <row r="265" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+    </row>
+    <row r="266" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+    </row>
+    <row r="267" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+    </row>
+    <row r="268" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+    </row>
+    <row r="269" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+    </row>
+    <row r="271" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+    </row>
+    <row r="272" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+    </row>
+    <row r="273" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+    </row>
+    <row r="274" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+    </row>
+    <row r="275" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+    </row>
+    <row r="276" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+    </row>
+    <row r="277" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+    </row>
+    <row r="278" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+    </row>
+    <row r="279" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+    </row>
+    <row r="280" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+    </row>
+    <row r="281" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+    </row>
+    <row r="282" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+    </row>
+    <row r="283" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+    </row>
+    <row r="284" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+    </row>
+    <row r="285" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+    </row>
+    <row r="286" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+    </row>
+    <row r="287" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+    </row>
+    <row r="288" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+    </row>
+    <row r="289" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+    </row>
+    <row r="291" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+    </row>
+    <row r="292" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+    </row>
+    <row r="293" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+    </row>
+    <row r="294" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+    </row>
+    <row r="295" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18243,13 +18488,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -18294,7 +18539,7 @@
         <v>1.2279085192200808E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -18339,7 +18584,7 @@
         <v>0.70533132928470998</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -18374,7 +18619,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -18409,7 +18654,7 @@
         <v>0.17086804073973499</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -18444,7 +18689,7 @@
         <v>0.171697248433512</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -18479,7 +18724,7 @@
         <v>0.17443666559002999</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -18514,7 +18759,7 @@
         <v>0.17690051952166999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -18549,7 +18794,7 @@
         <v>0.17654554655181801</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -18578,7 +18823,7 @@
         <v>0.17411860264206899</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -18607,7 +18852,7 @@
         <v>0.175935205113702</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -18636,7 +18881,7 @@
         <v>0.17427622300988699</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -18665,7 +18910,7 @@
         <v>0.17224969239811899</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -18694,7 +18939,7 @@
         <v>0.17435257559575301</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -18723,7 +18968,7 @@
         <v>0.171222354567128</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -18752,7 +18997,7 @@
         <v>0.17230494746765301</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -18781,7 +19026,7 @@
         <v>0.17976030708667101</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -18810,7 +19055,7 @@
         <v>0.174433801903358</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -18839,7 +19084,7 @@
         <v>0.17714435708530099</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -18865,7 +19110,7 @@
         <v>0.17371638201273101</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -18888,7 +19133,7 @@
         <v>0.17123203171632401</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -18911,7 +19156,7 @@
         <v>0.17318569822136001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -18934,7 +19179,7 @@
         <v>0.17669669700448201</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -18954,7 +19199,7 @@
         <v>0.25295075090609098</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
@@ -18971,7 +19216,7 @@
         <v>0.256452611497334</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -18988,7 +19233,7 @@
         <v>0.25868777299010298</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
@@ -19005,7 +19250,7 @@
         <v>0.2539674766801</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
@@ -19019,7 +19264,7 @@
         <v>0.25848980394328103</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
@@ -19033,7 +19278,7 @@
         <v>0.25493042534243598</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
@@ -19047,7 +19292,7 @@
         <v>0.25702073078272197</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
@@ -19061,7 +19306,7 @@
         <v>0.25281370286486299</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
@@ -19075,7 +19320,7 @@
         <v>0.25787828139437702</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
@@ -19089,7 +19334,7 @@
         <v>0.255030114263046</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
@@ -19103,7 +19348,7 @@
         <v>0.25326708245889501</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
@@ -19117,7 +19362,7 @@
         <v>0.25901851572451601</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>32</v>
       </c>
@@ -19128,7 +19373,7 @@
         <v>0.22249606599096799</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>33</v>
       </c>
@@ -19136,7 +19381,7 @@
         <v>0.22770140189949001</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>34</v>
       </c>
@@ -19144,7 +19389,7 @@
         <v>0.22467693879523801</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>35</v>
       </c>
@@ -19152,7 +19397,7 @@
         <v>0.22590951148508701</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>36</v>
       </c>
@@ -19170,12 +19415,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -19220,7 +19465,7 @@
         <v>5.1155359965755959E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -19265,7 +19510,7 @@
         <v>0.47681214118341592</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -19300,7 +19545,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -19335,7 +19580,7 @@
         <v>10.6539096425895</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -19370,7 +19615,7 @@
         <v>10.8579810008815</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -19405,7 +19650,7 @@
         <v>10.831312443746899</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -19440,7 +19685,7 @@
         <v>10.709515833036701</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -19475,7 +19720,7 @@
         <v>10.5903781690852</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -19504,7 +19749,7 @@
         <v>10.753363759575</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -19533,7 +19778,7 @@
         <v>10.653749196664901</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -19562,7 +19807,7 @@
         <v>10.8630753057798</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -19591,7 +19836,7 @@
         <v>10.7208205400928</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -19620,7 +19865,7 @@
         <v>10.6700806810118</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>11</v>
       </c>
@@ -19649,7 +19894,7 @@
         <v>10.6606574449491</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>12</v>
       </c>
@@ -19678,7 +19923,7 @@
         <v>10.8131728102025</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>13</v>
       </c>
@@ -19707,7 +19952,7 @@
         <v>10.8081420366551</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>14</v>
       </c>
@@ -19736,7 +19981,7 @@
         <v>10.586819027671799</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>15</v>
       </c>
@@ -19765,7 +20010,7 @@
         <v>10.7337029456849</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>16</v>
       </c>
@@ -19791,7 +20036,7 @@
         <v>10.7080767594852</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>17</v>
       </c>
@@ -19814,7 +20059,7 @@
         <v>10.6292015876151</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>18</v>
       </c>
@@ -19837,7 +20082,7 @@
         <v>10.6922490647235</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>19</v>
       </c>
@@ -19860,7 +20105,7 @@
         <v>10.661460418557301</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20</v>
       </c>
@@ -19880,7 +20125,7 @@
         <v>15.924948044130501</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>21</v>
       </c>
@@ -19897,7 +20142,7 @@
         <v>15.963192712237699</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>22</v>
       </c>
@@ -19914,7 +20159,7 @@
         <v>15.8676552218831</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>23</v>
       </c>
@@ -19931,7 +20176,7 @@
         <v>15.928435989248699</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>24</v>
       </c>
@@ -19945,7 +20190,7 @@
         <v>15.4712021433598</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>25</v>
       </c>
@@ -19959,7 +20204,7 @@
         <v>15.4267437621642</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>26</v>
       </c>
@@ -19973,7 +20218,7 @@
         <v>15.363023447442201</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>27</v>
       </c>
@@ -19987,7 +20232,7 @@
         <v>15.4784018893041</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>28</v>
       </c>
@@ -20001,7 +20246,7 @@
         <v>15.598700910453401</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>29</v>
       </c>
@@ -20015,7 +20260,7 @@
         <v>15.699463941581101</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>30</v>
       </c>
@@ -20029,7 +20274,7 @@
         <v>15.751226314712399</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>31</v>
       </c>
@@ -20043,7 +20288,7 @@
         <v>15.601321813860199</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>32</v>
       </c>
@@ -20054,7 +20299,7 @@
         <v>13.9597270287277</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>33</v>
       </c>
@@ -20062,7 +20307,7 @@
         <v>13.946102058433601</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>34</v>
       </c>
@@ -20070,7 +20315,7 @@
         <v>13.9823014618208</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>35</v>
       </c>
@@ -20078,7 +20323,7 @@
         <v>13.749906400784599</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>36</v>
       </c>

--- a/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
+++ b/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5562D9B-800E-4A8B-A55A-17EAFFE389C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CB86C3-BC88-4521-946B-C38277BB1D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Together" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="321">
   <si>
     <t>Date</t>
   </si>
@@ -813,6 +816,192 @@
   </si>
   <si>
     <t>estimated y error</t>
+  </si>
+  <si>
+    <t>Jun25,2026+4-10-12PM</t>
+  </si>
+  <si>
+    <t>Jun25,2026+4-19-56PM</t>
+  </si>
+  <si>
+    <t>Jun25,2026+4-49-20PM</t>
+  </si>
+  <si>
+    <t>Jun25,2026+5-08-43PM</t>
+  </si>
+  <si>
+    <t>Jun25,2026+5-19-57PM</t>
+  </si>
+  <si>
+    <t>Jun25,2026+5-27-48PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+10-56-35AM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+11-28-25AM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+11-36-33AM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+11-52-41AM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-03-36PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-12-49PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-20-44PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-29-09PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-42-26PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-50-28PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+12-58-38PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+1-37-18PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+1-55-20PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+2-03-34PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+2-27-49PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+2-36-47PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+2-47-54PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+2-58-11PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+3-06-07PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+3-31-59PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+4-14-20PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+4-22-14PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+4-33-29PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+4-53-29PM</t>
+  </si>
+  <si>
+    <t>Jun26,2026+5-09-29PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+8-54-37AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-03-42AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-24-49AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-32-44AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-40-52AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-48-39AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+9-56-40AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+10-24-54AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+11-53-47AM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+12-03-56PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+12-16-37PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+12-39-56PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+12-47-48PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+12-57-07PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+2-08-46PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+2-21-51PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+2-29-47PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+3-49-02PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+3-56-51PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+4-04-46PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+4-14-04PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+4-22-27PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+4-43-12PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+4-53-21PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-03-46PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-11-57PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-22-17PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-38-21PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-46-18PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+5-54-12PM</t>
+  </si>
+  <si>
+    <t>Jun29,2026+6-02-58PM</t>
   </si>
 </sst>
 </file>
@@ -2659,7 +2848,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2667,6 +2855,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4658,7 +4847,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4666,6 +4854,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4950,7 +5139,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4958,6 +5146,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4993,6 +5182,2256 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Alpha 456 vs Alpha 894</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'All Together'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Alpha 456</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'All Together'!$B$2:$B$233</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="232"/>
+                <c:pt idx="0">
+                  <c:v>8.1314875900026795</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2055994032900799</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.2176590050244904</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2690216688035498</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.2739805096279504</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.481531830496198</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.346083770183299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.452491695077299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18.351915434355199</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18.337397032620899</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18.232394257417202</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>18.415074041865601</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>18.341941017083698</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18.237027996635099</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18.531243546545401</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18.412716855394802</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18.4923898758226</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18.515382021503999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18.391192672959299</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>18.551612310419799</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>18.393990200449998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18.450034969079201</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18.408277105199002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.5185527459719204</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.5260980793629599</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.4894844505278897</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8.5701060942568006</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5447049809269604</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.4017872832855591</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.4035403242380404</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.5895120122534792</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.6524212475503699</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.2927304597387206</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.4368095561837997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8.6554109919161206</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.53551089338964</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.2121360213246692</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8.3727208112640206</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8.4364141305933895</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8.4084015562695207</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.5099572412062301</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.4321434520724008</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.4721216638779193</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.4953666075608503</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.7711252103094601</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.5801266895029205</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.5783681642005494</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8.6129268121772302</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8.6349505815443095</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8.5827352500219707</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8.6784045244654298</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8.5889121451567796</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>8.2237273067390202</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>8.26640584418465</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>8.2614937671479094</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7.0733851626533504</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.0645821415754702</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7.0594232243202404</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.0595369414161802</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7.1355028757261403</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7.1742988315936698</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7.2143004246012596</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7.1896716464449897</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>7.0740088746791701</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7.1243444840245997</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>7.0585349758452001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7.0753396553470003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>7.0929763944296802</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>7.1058506533772503</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>7.1002899790140797</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.0521776395148397</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.1167399746803</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7.1150966196750796</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.1580456374110897</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7.2190634878376496</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>7.2062880356903998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7.1744031277414697</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7.1782561712895996</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.1789296294298</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7.1380410516405304</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.1009576964689503</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>7.1095475512566804</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>7.1520505928297498</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>7.1324554911158904</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>7.1772995060305798</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>7.13962874760949</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>7.1606128880127899</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5.5657944042335004</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.4648667593817297</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.6047427761818804</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.5960936640263199</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5.4713363021862502</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5.5409104673644096</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5.55013048416959</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.5616342974163304</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.5301083552827803</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.4935494282478201</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.4627011461568502</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.5557750287565701</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.5014512688728496</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.4947589504036598</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.5489303201094904</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.4160645106972503</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>13.881207281537201</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>14.0895904209866</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>13.781524940490501</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>13.849983967959</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>14.1045893865774</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>14.045243904631301</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>14.041948410297801</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>13.9314720937797</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>13.939302031872</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>13.7686312681289</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>13.860947786333201</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>14.0288192886568</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>14.0564949797</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>13.967021506007001</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>13.8984865800428</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>13.7709959964952</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>13.7843547051184</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>13.808475282008599</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>14.015153400719299</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>14.0254740862873</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>13.9997618436749</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>14.019342208389499</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>13.970695398759901</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>13.907971630891801</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>13.8994236879669</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>14.055169741167299</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>13.9142762890247</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>13.841323444683701</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>13.804980095407201</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>13.884446951227901</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>13.963402223733601</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>13.9597270287277</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>13.946102058433601</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.9823014618208</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>13.749906400784599</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>13.720594247384501</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>15.5831740366148</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>15.6181213588261</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>15.471660411280601</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>15.4286358328345</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>15.725390191826</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>15.6295450777592</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>15.5447105698267</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>15.641779033917301</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>15.560241393406899</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>15.6798903930978</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>15.5257705053734</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>15.5068553708303</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>15.7245514226287</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>15.653971830187899</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>15.585241971938</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>15.591441713773801</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>15.513624662526899</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>15.550450799138201</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>15.5999990421973</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>15.5612294230614</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>15.389959627991299</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>15.6769168147221</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>15.516217850365001</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>15.4712021433598</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>15.4267437621642</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>15.363023447442201</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>15.4784018893041</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>15.598700910453401</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>15.699463941581101</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>15.751226314712399</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>15.601321813860199</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>15.893216524612599</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>15.779780400421799</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>15.7375098014318</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>15.644238135424301</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>16.0404007362275</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>15.526853103393799</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>15.7036096357806</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>15.562012023522399</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>15.913642252075</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>15.896285735356299</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>15.958659068376001</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>15.673134901285501</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>15.850053804713101</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>15.8642190956806</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>15.9252668940867</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>15.884348606860501</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>15.6346331521121</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>15.818170639051299</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>15.947264131374601</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>15.924948044130501</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>15.963192712237699</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>15.8676552218831</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>15.928435989248699</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>10.6515835159838</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>10.663341069103801</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>10.720671290806401</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>10.6070403098376</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>10.607916558495299</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>10.796548325563</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>10.8409786177823</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>10.772956842649499</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>10.6830303352735</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>10.585364148466899</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>10.5286364956397</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>10.6204309820713</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>10.6162779389606</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>10.775713711424901</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>10.7723544954987</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>10.7080767594852</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>10.6292015876151</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>10.6922490647235</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>10.661460418557301</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>10.794234615893799</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>10.8450661689269</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>10.7513220521733</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>10.544390346656099</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>10.7196028974402</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>10.753363759575</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>10.653749196664901</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>10.8630753057798</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>10.7208205400928</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>10.6700806810118</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>10.6606574449491</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>10.8131728102025</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>10.8081420366551</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>10.586819027671799</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>10.7337029456849</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>10.6539096425895</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>10.8579810008815</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>10.831312443746899</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>10.709515833036701</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>10.5903781690852</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'All Together'!$C$2:$C$233</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="232"/>
+                <c:pt idx="0">
+                  <c:v>0.17068222085432</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.169252380360598</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17600556016018701</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17477778117201601</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17496986858800301</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.39075425090921301</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39090251610402299</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38163793874347302</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.38646897393750201</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.38820632020412599</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.391100077546855</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.37812534333091802</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.38449528426413199</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.38779470041263903</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.378248054436716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.388322173460803</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.38881861759339797</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.39254780032303299</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.38860291038577099</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.391344107724999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.39401793952400199</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.398157579716993</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.38710256673105198</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.18265936593662399</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.17720413354468001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.183642067498062</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.18126642652018499</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17863631678412401</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.18200369359492499</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.18140063454570701</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.14198189433295499</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.14200693706074399</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.13879302222888601</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.14134057599559999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.14287369952523299</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.14242039757473199</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.13513280226965799</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.13504563445130599</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.13859780418944301</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.13768382280778599</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.137341027012235</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.14146322755453</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.1440878295095</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.139203017324112</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.14444988833485001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.14486186097849299</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.14493175120103199</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.14335784354365599</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.14372426788936199</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.140914458888726</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.144559929539015</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.13911305366694399</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.136881983671574</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.135891683439223</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.134600217130598</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.117218052017694</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.116738218899043</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.116641895814922</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.117986722306339</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.116363944216263</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.117960737624138</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.11777189549636199</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.118362346500101</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.11875028071223</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.118209453954305</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.116577694816434</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.117670638852321</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.118098845799444</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.11655919684067299</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.118487075826876</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.117049111989703</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.116964493443121</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.1174932059815</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.118724780988732</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.11857414162119</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.116857985488521</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.117839930521939</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.116123290748398</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.116339626646247</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.118521454357363</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.117743388207075</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.116823099810358</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.118509294607666</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.118631007440724</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.117484320873481</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.118251546607688</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.118181098472526</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>8.9287039240001795E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8.9953273584561996E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>9.1230909809772498E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>9.0037965159722497E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>9.2063662732121604E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>9.0566169869859395E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9.1281359996997199E-2</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>9.0246189977935598E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>8.7987770056780296E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>9.1038024594974204E-2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>9.0356969610468907E-2</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>8.9055177802521202E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>9.0556231765949805E-2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>9.1259865204828206E-2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>8.8371089308141498E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>8.9886315679026302E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.22378459935658199</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.228434718604688</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.221372998488612</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.225975457594905</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.225216837741747</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.229746279532067</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.22722518963626401</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.222965184868961</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.22898718060617901</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.22580668748875701</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.231594890582631</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.224583618990919</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.23249128317182099</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.23073510515949899</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.229179326874075</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.226024665246639</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.22988414195496401</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.22795719930278499</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.227267035209756</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.22728875634974799</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.22819660608103401</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.22449918198189101</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.22352994908158599</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.22753327784977401</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.22784419865740199</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.225433003733543</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.22712348211729699</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.22894109101944199</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.23027592968354901</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.22733899516780401</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.22718964047891599</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.22249606599096799</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.22770140189949001</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.22467693879523801</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.22590951148508701</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.22795873224990801</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.26064960163891099</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.25338188968269398</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.25038094455952498</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.256215228918099</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.25483329669185101</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.25854387484878599</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.25519336396030601</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.25663303680948102</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.25601459599486398</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.25648553124648299</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.25339182435774998</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.26261256236820102</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.25914013258546797</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.25187380012057398</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.25861462842520899</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.26412000142144099</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.25505739125523702</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.25268334549192301</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.254203134019032</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.25355249186689299</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.258640908855092</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.25176887581155899</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.25436276153236997</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.25848980394328103</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.25493042534243598</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.25702073078272197</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.25281370286486299</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.25787828139437702</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.255030114263046</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.25326708245889501</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.25901851572451601</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.25402214979933802</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.25207440807669201</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.25648835225167999</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>0.25619702232418301</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.256904989972564</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>0.25656545981822299</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.25471437628790899</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.25564492601438199</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.26266359379455601</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.25914186884267898</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.25621155685651098</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.25866494788723898</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.25801756322347102</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.25944545650678502</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.25336488450504602</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.261553420142073</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>0.26019522603942802</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.25868729407005198</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>0.25516460879894798</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>0.25295075090609098</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>0.256452611497334</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>0.25868777299010298</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>0.2539674766801</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0.17294771128421699</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>0.175665485735155</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>0.17382778027635701</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>0.17455983570099701</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>0.17664296551393399</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>0.17708531560420199</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>0.17557573140333699</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>0.173457649972002</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>0.17535865105134299</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.175039518424147</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.17459939950666101</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>0.17177387798819599</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.172049396498035</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>0.17416028353340501</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.17432866559164001</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>0.17371638201273101</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>0.17123203171632401</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>0.17318569822136001</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>0.17669669700448201</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>0.17723933870696301</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>0.17063092731327101</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.17490193092626999</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>0.17702310390171999</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.171948853936535</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>0.17411860264206899</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.175935205113702</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>0.17427622300988699</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.17224969239811899</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.17435257559575301</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.171222354567128</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.17230494746765301</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>0.17976030708667101</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>0.174433801903358</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>0.17714435708530099</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>0.17086804073973499</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>0.171697248433512</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.17443666559002999</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>0.17690051952166999</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>0.17654554655181801</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5A79-43C7-A012-327EE2E82A5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>new</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'All Together'!$B$236:$B$297</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>10.6221259181231</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.735748783007899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.566758158407101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10.631078078007899</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.634659592750699</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.672389702778499</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.624260123408201</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.518782041710701</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.635277697575599</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.703364754206801</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.6888204197401</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.707744909524299</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10.731647561909099</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10.743488692224201</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10.7190641789712</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10.7246119730962</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10.854434693120901</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.706374987729699</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.637698363317099</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10.739175433178</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.686605164880801</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>10.6515045746171</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10.701321936698699</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10.605269760878899</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>10.5803727434901</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>10.576268807422901</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>10.5196221348473</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>10.558405934335401</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>10.633836662036201</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>10.6134173334769</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>10.660587486404401</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>16.4455493987636</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>16.204494346869399</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>16.286326741643599</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>16.207702786854899</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>16.458700382311001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>16.462078937325401</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>16.471494559838</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>16.339485818946901</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>16.355055381852601</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>16.3595891765879</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>16.2164791072151</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>16.261548141097599</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>16.384810735183699</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>16.350623841514199</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>16.187723396986499</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>16.3038309514011</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>16.164613922247401</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>16.240097105116</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>16.2518971233978</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>16.381371335960701</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>16.378295734472999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>16.444871536786899</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>16.377685606618101</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16.370821349538001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16.147989198104199</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16.418772327555299</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16.352237501405199</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>16.311710862235199</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16.368589028451201</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>16.289962255694199</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16.347944436289598</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'All Together'!$C$236:$C$297</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="62"/>
+                <c:pt idx="0">
+                  <c:v>0.171876620266287</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17507983789020901</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17353748848485201</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17399520336378199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16979104098602099</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.175682517244173</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.17111359499762699</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.174442312499583</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.17165345419397299</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.17188594050678699</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.17182639857690499</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.173011271970926</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.173393882992014</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.17255170638235601</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.176156057962948</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.17277891898827699</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.173614948750792</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.17607067167010601</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.17040120856414201</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.17423160269966501</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.174369956316375</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.17111424613243301</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.174141819699693</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.17027613633024699</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.17305899861083601</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.169629744786672</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.17362236751906199</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.17378947989454699</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.17301730214639</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.17294290042990301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.17314296764265499</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.26702709086345899</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.26377604366503299</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.26272554597887199</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.26788317969509901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.26503400399869398</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.26673897966627602</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.26807575946030698</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.266570039729353</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.27166172606546901</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.26522605962651602</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.27094063293660098</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.26838563360762802</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.26226006746867903</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.26283415625491802</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.265891536409124</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.26086999753535101</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.264030412441006</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.26104421609513101</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.26790761730572898</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.26200964452208297</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.26657014430711701</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.264335730958146</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.26876048744697101</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.26514897700620299</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.26219390887345601</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.26184487099436499</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.26409583467590397</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.26424448419416702</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.26363414452799</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.26464837628465498</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.27030866825799199</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5A79-43C7-A012-327EE2E82A5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="9231519"/>
+        <c:axId val="9232479"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="9231519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>894 Coefficient</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9232479"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="9232479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>456 Coefficient</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9231519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7530,7 +9969,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7538,6 +9976,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7572,7 +10011,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7998,7 +10437,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -8006,6 +10444,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8040,7 +10479,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -10578,7 +13017,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10586,6 +13024,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10620,7 +13059,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -11079,7 +13518,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11087,6 +13525,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11401,6 +13840,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -15013,20 +17492,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>491226</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>527170</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1075306</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>545142</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>117056</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>380399</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>233872</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>398371</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -15118,6 +18113,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>853656</xdr:colOff>
+      <xdr:row>256</xdr:row>
+      <xdr:rowOff>503207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>530165</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>122804</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9CB689C-6724-419A-B444-E34469C8F67A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -15543,13 +18576,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P295"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P298"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15590,7 +18623,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15644,7 +18677,7 @@
         <v>5.1155359965755959E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -15698,7 +18731,7 @@
         <v>1.2279085192200808E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -15712,7 +18745,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -15723,7 +18756,7 @@
         <v>0.17477778117201601</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -15734,7 +18767,7 @@
         <v>0.17496986858800301</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -15745,7 +18778,7 @@
         <v>0.39075425090921301</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -15756,7 +18789,7 @@
         <v>0.39090251610402299</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -15767,7 +18800,7 @@
         <v>0.38163793874347302</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -15778,7 +18811,7 @@
         <v>0.38646897393750201</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -15789,7 +18822,7 @@
         <v>0.38820632020412599</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -15800,7 +18833,7 @@
         <v>0.391100077546855</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -15811,7 +18844,7 @@
         <v>0.37812534333091802</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -15822,7 +18855,7 @@
         <v>0.38449528426413199</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -15833,7 +18866,7 @@
         <v>0.38779470041263903</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -15844,7 +18877,7 @@
         <v>0.378248054436716</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -15855,7 +18888,7 @@
         <v>0.388322173460803</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -15866,7 +18899,7 @@
         <v>0.38881861759339797</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -15877,7 +18910,7 @@
         <v>0.39254780032303299</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -15888,7 +18921,7 @@
         <v>0.38860291038577099</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -15899,7 +18932,7 @@
         <v>0.391344107724999</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -15910,7 +18943,7 @@
         <v>0.39401793952400199</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -15921,7 +18954,7 @@
         <v>0.398157579716993</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -15932,7 +18965,7 @@
         <v>0.38710256673105198</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -15943,7 +18976,7 @@
         <v>0.18265936593662399</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -15954,7 +18987,7 @@
         <v>0.17720413354468001</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -15965,7 +18998,7 @@
         <v>0.183642067498062</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -15976,7 +19009,7 @@
         <v>0.18126642652018499</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -15987,7 +19020,7 @@
         <v>0.17863631678412401</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -15998,7 +19031,7 @@
         <v>0.18200369359492499</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -16009,7 +19042,7 @@
         <v>0.18140063454570701</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -16020,7 +19053,7 @@
         <v>0.14198189433295499</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -16031,7 +19064,7 @@
         <v>0.14200693706074399</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -16042,7 +19075,7 @@
         <v>0.13879302222888601</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -16053,7 +19086,7 @@
         <v>0.14134057599559999</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -16064,7 +19097,7 @@
         <v>0.14287369952523299</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -16075,7 +19108,7 @@
         <v>0.14242039757473199</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -16086,7 +19119,7 @@
         <v>0.13513280226965799</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -16097,7 +19130,7 @@
         <v>0.13504563445130599</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -16108,7 +19141,7 @@
         <v>0.13859780418944301</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -16119,7 +19152,7 @@
         <v>0.13768382280778599</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -16130,7 +19163,7 @@
         <v>0.137341027012235</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -16141,7 +19174,7 @@
         <v>0.14146322755453</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -16152,7 +19185,7 @@
         <v>0.1440878295095</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -16163,7 +19196,7 @@
         <v>0.139203017324112</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -16174,7 +19207,7 @@
         <v>0.14444988833485001</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -16185,7 +19218,7 @@
         <v>0.14486186097849299</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -16196,7 +19229,7 @@
         <v>0.14493175120103199</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
@@ -16207,7 +19240,7 @@
         <v>0.14335784354365599</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -16218,7 +19251,7 @@
         <v>0.14372426788936199</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -16229,7 +19262,7 @@
         <v>0.140914458888726</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -16240,7 +19273,7 @@
         <v>0.144559929539015</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -16251,7 +19284,7 @@
         <v>0.13911305366694399</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
@@ -16262,7 +19295,7 @@
         <v>0.136881983671574</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -16273,7 +19306,7 @@
         <v>0.135891683439223</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -16284,7 +19317,7 @@
         <v>0.134600217130598</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
@@ -16295,7 +19328,7 @@
         <v>0.117218052017694</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -16306,7 +19339,7 @@
         <v>0.116738218899043</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
@@ -16317,7 +19350,7 @@
         <v>0.116641895814922</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -16328,7 +19361,7 @@
         <v>0.117986722306339</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -16339,7 +19372,7 @@
         <v>0.116363944216263</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
@@ -16350,7 +19383,7 @@
         <v>0.117960737624138</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -16361,7 +19394,7 @@
         <v>0.11777189549636199</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -16372,7 +19405,7 @@
         <v>0.118362346500101</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -16383,7 +19416,7 @@
         <v>0.11875028071223</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
@@ -16394,7 +19427,7 @@
         <v>0.118209453954305</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
@@ -16405,7 +19438,7 @@
         <v>0.116577694816434</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -16416,7 +19449,7 @@
         <v>0.117670638852321</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
@@ -16427,7 +19460,7 @@
         <v>0.118098845799444</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -16438,7 +19471,7 @@
         <v>0.11655919684067299</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
@@ -16449,7 +19482,7 @@
         <v>0.118487075826876</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
@@ -16460,7 +19493,7 @@
         <v>0.117049111989703</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
@@ -16471,7 +19504,7 @@
         <v>0.116964493443121</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -16482,7 +19515,7 @@
         <v>0.1174932059815</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
@@ -16493,7 +19526,7 @@
         <v>0.118724780988732</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
@@ -16504,7 +19537,7 @@
         <v>0.11857414162119</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
@@ -16515,7 +19548,7 @@
         <v>0.116857985488521</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
@@ -16526,7 +19559,7 @@
         <v>0.117839930521939</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
@@ -16537,7 +19570,7 @@
         <v>0.116123290748398</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
@@ -16548,7 +19581,7 @@
         <v>0.116339626646247</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
@@ -16559,7 +19592,7 @@
         <v>0.118521454357363</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -16570,7 +19603,7 @@
         <v>0.117743388207075</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -16581,7 +19614,7 @@
         <v>0.116823099810358</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
@@ -16592,7 +19625,7 @@
         <v>0.118509294607666</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
@@ -16603,7 +19636,7 @@
         <v>0.118631007440724</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
@@ -16614,7 +19647,7 @@
         <v>0.117484320873481</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -16625,7 +19658,7 @@
         <v>0.118251546607688</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -16636,7 +19669,7 @@
         <v>0.118181098472526</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
@@ -16647,7 +19680,7 @@
         <v>8.9287039240001795E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -16658,7 +19691,7 @@
         <v>8.9953273584561996E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
@@ -16669,7 +19702,7 @@
         <v>9.1230909809772498E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -16680,7 +19713,7 @@
         <v>9.0037965159722497E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -16691,7 +19724,7 @@
         <v>9.2063662732121604E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
@@ -16702,7 +19735,7 @@
         <v>9.0566169869859395E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
@@ -16713,7 +19746,7 @@
         <v>9.1281359996997199E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
@@ -16724,7 +19757,7 @@
         <v>9.0246189977935598E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
@@ -16735,7 +19768,7 @@
         <v>8.7987770056780296E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
@@ -16746,7 +19779,7 @@
         <v>9.1038024594974204E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
@@ -16757,7 +19790,7 @@
         <v>9.0356969610468907E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -16768,7 +19801,7 @@
         <v>8.9055177802521202E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
@@ -16779,7 +19812,7 @@
         <v>9.0556231765949805E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -16790,7 +19823,7 @@
         <v>9.1259865204828206E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
@@ -16801,7 +19834,7 @@
         <v>8.8371089308141498E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
@@ -16812,7 +19845,7 @@
         <v>8.9886315679026302E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -16823,7 +19856,7 @@
         <v>0.22378459935658199</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
@@ -16834,7 +19867,7 @@
         <v>0.228434718604688</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
@@ -16845,7 +19878,7 @@
         <v>0.221372998488612</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
@@ -16856,7 +19889,7 @@
         <v>0.225975457594905</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
@@ -16867,7 +19900,7 @@
         <v>0.225216837741747</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
@@ -16878,7 +19911,7 @@
         <v>0.229746279532067</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
@@ -16889,7 +19922,7 @@
         <v>0.22722518963626401</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
@@ -16900,7 +19933,7 @@
         <v>0.222965184868961</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
@@ -16911,7 +19944,7 @@
         <v>0.22898718060617901</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
@@ -16922,7 +19955,7 @@
         <v>0.22580668748875701</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>116</v>
       </c>
@@ -16933,7 +19966,7 @@
         <v>0.231594890582631</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
@@ -16944,7 +19977,7 @@
         <v>0.224583618990919</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
@@ -16955,7 +19988,7 @@
         <v>0.23249128317182099</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
@@ -16966,7 +19999,7 @@
         <v>0.23073510515949899</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
@@ -16977,7 +20010,7 @@
         <v>0.229179326874075</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>121</v>
       </c>
@@ -16988,7 +20021,7 @@
         <v>0.226024665246639</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>122</v>
       </c>
@@ -16999,7 +20032,7 @@
         <v>0.22988414195496401</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>123</v>
       </c>
@@ -17010,7 +20043,7 @@
         <v>0.22795719930278499</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
@@ -17021,7 +20054,7 @@
         <v>0.227267035209756</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>125</v>
       </c>
@@ -17032,7 +20065,7 @@
         <v>0.22728875634974799</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>126</v>
       </c>
@@ -17043,7 +20076,7 @@
         <v>0.22819660608103401</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>127</v>
       </c>
@@ -17054,7 +20087,7 @@
         <v>0.22449918198189101</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>128</v>
       </c>
@@ -17065,7 +20098,7 @@
         <v>0.22352994908158599</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
@@ -17076,7 +20109,7 @@
         <v>0.22753327784977401</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
@@ -17087,7 +20120,7 @@
         <v>0.22784419865740199</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
@@ -17098,7 +20131,7 @@
         <v>0.225433003733543</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
@@ -17109,7 +20142,7 @@
         <v>0.22712348211729699</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
@@ -17120,7 +20153,7 @@
         <v>0.22894109101944199</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
@@ -17131,7 +20164,7 @@
         <v>0.23027592968354901</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
@@ -17142,7 +20175,7 @@
         <v>0.22733899516780401</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
@@ -17153,7 +20186,7 @@
         <v>0.22718964047891599</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
@@ -17164,7 +20197,7 @@
         <v>0.22249606599096799</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
@@ -17175,7 +20208,7 @@
         <v>0.22770140189949001</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
@@ -17186,7 +20219,7 @@
         <v>0.22467693879523801</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
@@ -17197,7 +20230,7 @@
         <v>0.22590951148508701</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
@@ -17208,7 +20241,7 @@
         <v>0.22795873224990801</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
@@ -17219,7 +20252,7 @@
         <v>0.26064960163891099</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
@@ -17230,7 +20263,7 @@
         <v>0.25338188968269398</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
@@ -17241,7 +20274,7 @@
         <v>0.25038094455952498</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
@@ -17252,7 +20285,7 @@
         <v>0.256215228918099</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
@@ -17263,7 +20296,7 @@
         <v>0.25483329669185101</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
@@ -17274,7 +20307,7 @@
         <v>0.25854387484878599</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
@@ -17285,7 +20318,7 @@
         <v>0.25519336396030601</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -17296,7 +20329,7 @@
         <v>0.25663303680948102</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
@@ -17307,7 +20340,7 @@
         <v>0.25601459599486398</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
@@ -17318,7 +20351,7 @@
         <v>0.25648553124648299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
@@ -17329,7 +20362,7 @@
         <v>0.25339182435774998</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
@@ -17340,7 +20373,7 @@
         <v>0.26261256236820102</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
@@ -17351,7 +20384,7 @@
         <v>0.25914013258546797</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
@@ -17362,7 +20395,7 @@
         <v>0.25187380012057398</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
@@ -17373,7 +20406,7 @@
         <v>0.25861462842520899</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
@@ -17384,7 +20417,7 @@
         <v>0.26412000142144099</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
@@ -17395,7 +20428,7 @@
         <v>0.25505739125523702</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
@@ -17406,7 +20439,7 @@
         <v>0.25268334549192301</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
@@ -17417,7 +20450,7 @@
         <v>0.254203134019032</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
@@ -17428,7 +20461,7 @@
         <v>0.25355249186689299</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
@@ -17439,7 +20472,7 @@
         <v>0.258640908855092</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
@@ -17450,7 +20483,7 @@
         <v>0.25176887581155899</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
@@ -17461,7 +20494,7 @@
         <v>0.25436276153236997</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
@@ -17472,7 +20505,7 @@
         <v>0.25848980394328103</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
@@ -17483,7 +20516,7 @@
         <v>0.25493042534243598</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
@@ -17494,7 +20527,7 @@
         <v>0.25702073078272197</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
@@ -17505,7 +20538,7 @@
         <v>0.25281370286486299</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
@@ -17516,7 +20549,7 @@
         <v>0.25787828139437702</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
@@ -17527,7 +20560,7 @@
         <v>0.255030114263046</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
@@ -17538,7 +20571,7 @@
         <v>0.25326708245889501</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -17549,7 +20582,7 @@
         <v>0.25901851572451601</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>173</v>
       </c>
@@ -17560,7 +20593,7 @@
         <v>0.25402214979933802</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>174</v>
       </c>
@@ -17571,7 +20604,7 @@
         <v>0.25207440807669201</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>175</v>
       </c>
@@ -17582,7 +20615,7 @@
         <v>0.25648835225167999</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
@@ -17593,7 +20626,7 @@
         <v>0.25619702232418301</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>177</v>
       </c>
@@ -17604,7 +20637,7 @@
         <v>0.256904989972564</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>178</v>
       </c>
@@ -17615,7 +20648,7 @@
         <v>0.25656545981822299</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>179</v>
       </c>
@@ -17626,7 +20659,7 @@
         <v>0.25471437628790899</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>180</v>
       </c>
@@ -17637,7 +20670,7 @@
         <v>0.25564492601438199</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>181</v>
       </c>
@@ -17648,7 +20681,7 @@
         <v>0.26266359379455601</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>182</v>
       </c>
@@ -17659,7 +20692,7 @@
         <v>0.25914186884267898</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>183</v>
       </c>
@@ -17670,7 +20703,7 @@
         <v>0.25621155685651098</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>184</v>
       </c>
@@ -17681,7 +20714,7 @@
         <v>0.25866494788723898</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>185</v>
       </c>
@@ -17692,7 +20725,7 @@
         <v>0.25801756322347102</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>186</v>
       </c>
@@ -17703,7 +20736,7 @@
         <v>0.25944545650678502</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>187</v>
       </c>
@@ -17714,7 +20747,7 @@
         <v>0.25336488450504602</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>188</v>
       </c>
@@ -17725,7 +20758,7 @@
         <v>0.261553420142073</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>189</v>
       </c>
@@ -17736,7 +20769,7 @@
         <v>0.26019522603942802</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>190</v>
       </c>
@@ -17747,7 +20780,7 @@
         <v>0.25868729407005198</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>191</v>
       </c>
@@ -17758,7 +20791,7 @@
         <v>0.25516460879894798</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
@@ -17769,7 +20802,7 @@
         <v>0.25295075090609098</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>193</v>
       </c>
@@ -17780,7 +20813,7 @@
         <v>0.256452611497334</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>194</v>
       </c>
@@ -17791,7 +20824,7 @@
         <v>0.25868777299010298</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
@@ -17802,7 +20835,7 @@
         <v>0.2539674766801</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
@@ -17813,7 +20846,7 @@
         <v>0.17294771128421699</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>197</v>
       </c>
@@ -17824,7 +20857,7 @@
         <v>0.175665485735155</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>198</v>
       </c>
@@ -17835,7 +20868,7 @@
         <v>0.17382778027635701</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>199</v>
       </c>
@@ -17846,7 +20879,7 @@
         <v>0.17455983570099701</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>200</v>
       </c>
@@ -17857,7 +20890,7 @@
         <v>0.17664296551393399</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>201</v>
       </c>
@@ -17868,7 +20901,7 @@
         <v>0.17708531560420199</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>202</v>
       </c>
@@ -17879,7 +20912,7 @@
         <v>0.17557573140333699</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>203</v>
       </c>
@@ -17890,7 +20923,7 @@
         <v>0.173457649972002</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>204</v>
       </c>
@@ -17901,7 +20934,7 @@
         <v>0.17535865105134299</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>205</v>
       </c>
@@ -17912,7 +20945,7 @@
         <v>0.175039518424147</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>206</v>
       </c>
@@ -17923,7 +20956,7 @@
         <v>0.17459939950666101</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>207</v>
       </c>
@@ -17934,7 +20967,7 @@
         <v>0.17177387798819599</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>208</v>
       </c>
@@ -17945,7 +20978,7 @@
         <v>0.172049396498035</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>209</v>
       </c>
@@ -17956,7 +20989,7 @@
         <v>0.17416028353340501</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>210</v>
       </c>
@@ -17967,7 +21000,7 @@
         <v>0.17432866559164001</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>211</v>
       </c>
@@ -17978,7 +21011,7 @@
         <v>0.17371638201273101</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>212</v>
       </c>
@@ -17989,7 +21022,7 @@
         <v>0.17123203171632401</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>213</v>
       </c>
@@ -18000,7 +21033,7 @@
         <v>0.17318569822136001</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>214</v>
       </c>
@@ -18011,7 +21044,7 @@
         <v>0.17669669700448201</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>215</v>
       </c>
@@ -18022,7 +21055,7 @@
         <v>0.17723933870696301</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>216</v>
       </c>
@@ -18033,7 +21066,7 @@
         <v>0.17063092731327101</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>217</v>
       </c>
@@ -18044,7 +21077,7 @@
         <v>0.17490193092626999</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>218</v>
       </c>
@@ -18055,7 +21088,7 @@
         <v>0.17702310390171999</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>219</v>
       </c>
@@ -18066,7 +21099,7 @@
         <v>0.171948853936535</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>220</v>
       </c>
@@ -18077,7 +21110,7 @@
         <v>0.17411860264206899</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>221</v>
       </c>
@@ -18088,7 +21121,7 @@
         <v>0.175935205113702</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>222</v>
       </c>
@@ -18099,7 +21132,7 @@
         <v>0.17427622300988699</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>223</v>
       </c>
@@ -18110,7 +21143,7 @@
         <v>0.17224969239811899</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>224</v>
       </c>
@@ -18121,7 +21154,7 @@
         <v>0.17435257559575301</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>225</v>
       </c>
@@ -18132,7 +21165,7 @@
         <v>0.171222354567128</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>226</v>
       </c>
@@ -18143,7 +21176,7 @@
         <v>0.17230494746765301</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>227</v>
       </c>
@@ -18154,7 +21187,7 @@
         <v>0.17976030708667101</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>228</v>
       </c>
@@ -18165,7 +21198,7 @@
         <v>0.174433801903358</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>229</v>
       </c>
@@ -18176,7 +21209,7 @@
         <v>0.17714435708530099</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>230</v>
       </c>
@@ -18187,7 +21220,7 @@
         <v>0.17086804073973499</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>231</v>
       </c>
@@ -18198,7 +21231,7 @@
         <v>0.171697248433512</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>232</v>
       </c>
@@ -18209,7 +21242,7 @@
         <v>0.17443666559002999</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>233</v>
       </c>
@@ -18220,7 +21253,7 @@
         <v>0.17690051952166999</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>234</v>
       </c>
@@ -18231,253 +21264,699 @@
         <v>0.17654554655181801</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-    </row>
-    <row r="241" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
-    </row>
-    <row r="242" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-    </row>
-    <row r="243" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
-    </row>
-    <row r="244" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-    </row>
-    <row r="245" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-    </row>
-    <row r="246" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
-    </row>
-    <row r="247" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
-    </row>
-    <row r="248" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-    </row>
-    <row r="249" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-    </row>
-    <row r="250" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-    </row>
-    <row r="251" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-    </row>
-    <row r="252" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-    </row>
-    <row r="253" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-    </row>
-    <row r="254" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-    </row>
-    <row r="255" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
-    </row>
-    <row r="256" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-    </row>
-    <row r="257" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
-    </row>
-    <row r="258" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-    </row>
-    <row r="259" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-    </row>
-    <row r="260" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-    </row>
-    <row r="261" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
-    </row>
-    <row r="262" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
-    </row>
-    <row r="263" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
-    </row>
-    <row r="264" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
-    </row>
-    <row r="265" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B265" s="1"/>
-      <c r="C265" s="1"/>
-    </row>
-    <row r="266" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B266" s="1"/>
-      <c r="C266" s="1"/>
-    </row>
-    <row r="267" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
-    </row>
-    <row r="268" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B268" s="1"/>
-      <c r="C268" s="1"/>
-    </row>
-    <row r="269" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
-    </row>
-    <row r="270" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B270" s="1"/>
-      <c r="C270" s="1"/>
-    </row>
-    <row r="271" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
-    </row>
-    <row r="272" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-    </row>
-    <row r="273" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
-    </row>
-    <row r="274" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
-    </row>
-    <row r="275" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-    </row>
-    <row r="276" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-    </row>
-    <row r="277" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-    </row>
-    <row r="278" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
-    </row>
-    <row r="279" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
-    </row>
-    <row r="280" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
-    </row>
-    <row r="281" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
-    </row>
-    <row r="282" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
-    </row>
-    <row r="283" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B283" s="1"/>
-      <c r="C283" s="1"/>
-    </row>
-    <row r="284" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B284" s="1"/>
-      <c r="C284" s="1"/>
-    </row>
-    <row r="285" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
-    </row>
-    <row r="286" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
-    </row>
-    <row r="287" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
-    </row>
-    <row r="288" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B288" s="1"/>
-      <c r="C288" s="1"/>
-    </row>
-    <row r="289" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B289" s="1"/>
-      <c r="C289" s="1"/>
-    </row>
-    <row r="290" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B290" s="1"/>
-      <c r="C290" s="1"/>
-    </row>
-    <row r="291" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B291" s="1"/>
-      <c r="C291" s="1"/>
-    </row>
-    <row r="292" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B292" s="1"/>
-      <c r="C292" s="1"/>
-    </row>
-    <row r="293" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B293" s="1"/>
-      <c r="C293" s="1"/>
-    </row>
-    <row r="294" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
-    </row>
-    <row r="295" spans="2:3" x14ac:dyDescent="0.35">
-      <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
+    <row r="236" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B236" s="1">
+        <v>10.6221259181231</v>
+      </c>
+      <c r="C236" s="1">
+        <v>0.171876620266287</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B237" s="1">
+        <v>10.735748783007899</v>
+      </c>
+      <c r="C237" s="1">
+        <v>0.17507983789020901</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B238" s="1">
+        <v>10.566758158407101</v>
+      </c>
+      <c r="C238" s="1">
+        <v>0.17353748848485201</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B239" s="1">
+        <v>10.631078078007899</v>
+      </c>
+      <c r="C239" s="1">
+        <v>0.17399520336378199</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A240" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B240" s="1">
+        <v>10.634659592750699</v>
+      </c>
+      <c r="C240" s="1">
+        <v>0.16979104098602099</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A241" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B241" s="1">
+        <v>10.672389702778499</v>
+      </c>
+      <c r="C241" s="1">
+        <v>0.175682517244173</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A242" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B242" s="1">
+        <v>10.624260123408201</v>
+      </c>
+      <c r="C242" s="1">
+        <v>0.17111359499762699</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B243" s="1">
+        <v>10.518782041710701</v>
+      </c>
+      <c r="C243" s="1">
+        <v>0.174442312499583</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A244" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B244" s="1">
+        <v>10.635277697575599</v>
+      </c>
+      <c r="C244" s="1">
+        <v>0.17165345419397299</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A245" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B245" s="1">
+        <v>10.703364754206801</v>
+      </c>
+      <c r="C245" s="1">
+        <v>0.17188594050678699</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A246" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B246" s="1">
+        <v>10.6888204197401</v>
+      </c>
+      <c r="C246" s="1">
+        <v>0.17182639857690499</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B247" s="1">
+        <v>10.707744909524299</v>
+      </c>
+      <c r="C247" s="1">
+        <v>0.173011271970926</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B248" s="1">
+        <v>10.731647561909099</v>
+      </c>
+      <c r="C248" s="1">
+        <v>0.173393882992014</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A249" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B249" s="1">
+        <v>10.743488692224201</v>
+      </c>
+      <c r="C249" s="1">
+        <v>0.17255170638235601</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B250" s="1">
+        <v>10.7190641789712</v>
+      </c>
+      <c r="C250" s="1">
+        <v>0.176156057962948</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A251" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B251" s="1">
+        <v>10.7246119730962</v>
+      </c>
+      <c r="C251" s="1">
+        <v>0.17277891898827699</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A252" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B252" s="1">
+        <v>10.854434693120901</v>
+      </c>
+      <c r="C252" s="1">
+        <v>0.173614948750792</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A253" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B253" s="1">
+        <v>10.706374987729699</v>
+      </c>
+      <c r="C253" s="1">
+        <v>0.17607067167010601</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A254" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B254" s="1">
+        <v>10.637698363317099</v>
+      </c>
+      <c r="C254" s="1">
+        <v>0.17040120856414201</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A255" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B255" s="1">
+        <v>10.739175433178</v>
+      </c>
+      <c r="C255" s="1">
+        <v>0.17423160269966501</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A256" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B256" s="1">
+        <v>10.686605164880801</v>
+      </c>
+      <c r="C256" s="1">
+        <v>0.174369956316375</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A257" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B257" s="1">
+        <v>10.6515045746171</v>
+      </c>
+      <c r="C257" s="1">
+        <v>0.17111424613243301</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A258" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B258" s="1">
+        <v>10.701321936698699</v>
+      </c>
+      <c r="C258" s="1">
+        <v>0.174141819699693</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A259" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B259" s="1">
+        <v>10.605269760878899</v>
+      </c>
+      <c r="C259" s="1">
+        <v>0.17027613633024699</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A260" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B260" s="1">
+        <v>10.5803727434901</v>
+      </c>
+      <c r="C260" s="1">
+        <v>0.17305899861083601</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A261" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B261" s="1">
+        <v>10.576268807422901</v>
+      </c>
+      <c r="C261" s="1">
+        <v>0.169629744786672</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A262" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B262" s="1">
+        <v>10.5196221348473</v>
+      </c>
+      <c r="C262" s="1">
+        <v>0.17362236751906199</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A263" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B263" s="1">
+        <v>10.558405934335401</v>
+      </c>
+      <c r="C263" s="1">
+        <v>0.17378947989454699</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A264" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B264" s="1">
+        <v>10.633836662036201</v>
+      </c>
+      <c r="C264" s="1">
+        <v>0.17301730214639</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A265" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B265" s="1">
+        <v>10.6134173334769</v>
+      </c>
+      <c r="C265" s="1">
+        <v>0.17294290042990301</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B266" s="1">
+        <v>10.660587486404401</v>
+      </c>
+      <c r="C266" s="1">
+        <v>0.17314296764265499</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A267" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B267" s="1">
+        <v>16.4455493987636</v>
+      </c>
+      <c r="C267" s="1">
+        <v>0.26702709086345899</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A268" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B268" s="1">
+        <v>16.204494346869399</v>
+      </c>
+      <c r="C268" s="1">
+        <v>0.26377604366503299</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A269" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B269" s="1">
+        <v>16.286326741643599</v>
+      </c>
+      <c r="C269" s="1">
+        <v>0.26272554597887199</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A270" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B270" s="1">
+        <v>16.207702786854899</v>
+      </c>
+      <c r="C270" s="1">
+        <v>0.26788317969509901</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A271" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B271" s="1">
+        <v>16.458700382311001</v>
+      </c>
+      <c r="C271" s="1">
+        <v>0.26503400399869398</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A272" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B272" s="1">
+        <v>16.462078937325401</v>
+      </c>
+      <c r="C272" s="1">
+        <v>0.26673897966627602</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B273" s="1">
+        <v>16.471494559838</v>
+      </c>
+      <c r="C273" s="1">
+        <v>0.26807575946030698</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B274" s="1">
+        <v>16.339485818946901</v>
+      </c>
+      <c r="C274" s="1">
+        <v>0.266570039729353</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A275" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B275" s="1">
+        <v>16.355055381852601</v>
+      </c>
+      <c r="C275" s="1">
+        <v>0.27166172606546901</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A276" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B276" s="1">
+        <v>16.3595891765879</v>
+      </c>
+      <c r="C276" s="1">
+        <v>0.26522605962651602</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A277" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B277" s="1">
+        <v>16.2164791072151</v>
+      </c>
+      <c r="C277" s="1">
+        <v>0.27094063293660098</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A278" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B278" s="1">
+        <v>16.261548141097599</v>
+      </c>
+      <c r="C278" s="1">
+        <v>0.26838563360762802</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A279" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B279" s="1">
+        <v>16.384810735183699</v>
+      </c>
+      <c r="C279" s="1">
+        <v>0.26226006746867903</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A280" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B280" s="1">
+        <v>16.350623841514199</v>
+      </c>
+      <c r="C280" s="1">
+        <v>0.26283415625491802</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A281" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B281" s="1">
+        <v>16.187723396986499</v>
+      </c>
+      <c r="C281" s="1">
+        <v>0.265891536409124</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A282" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B282" s="1">
+        <v>16.3038309514011</v>
+      </c>
+      <c r="C282" s="1">
+        <v>0.26086999753535101</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A283" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B283" s="1">
+        <v>16.164613922247401</v>
+      </c>
+      <c r="C283" s="1">
+        <v>0.264030412441006</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B284" s="1">
+        <v>16.240097105116</v>
+      </c>
+      <c r="C284" s="1">
+        <v>0.26104421609513101</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A285" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B285" s="1">
+        <v>16.2518971233978</v>
+      </c>
+      <c r="C285" s="1">
+        <v>0.26790761730572898</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A286" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B286" s="1">
+        <v>16.381371335960701</v>
+      </c>
+      <c r="C286" s="1">
+        <v>0.26200964452208297</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A287" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B287" s="1">
+        <v>16.378295734472999</v>
+      </c>
+      <c r="C287" s="1">
+        <v>0.26657014430711701</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A288" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B288" s="1">
+        <v>16.444871536786899</v>
+      </c>
+      <c r="C288" s="1">
+        <v>0.264335730958146</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A289" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B289" s="1">
+        <v>16.377685606618101</v>
+      </c>
+      <c r="C289" s="1">
+        <v>0.26876048744697101</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B290" s="1">
+        <v>16.370821349538001</v>
+      </c>
+      <c r="C290" s="1">
+        <v>0.26514897700620299</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A291" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B291" s="1">
+        <v>16.147989198104199</v>
+      </c>
+      <c r="C291" s="1">
+        <v>0.26219390887345601</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A292" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B292" s="1">
+        <v>16.418772327555299</v>
+      </c>
+      <c r="C292" s="1">
+        <v>0.26184487099436499</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A293" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B293" s="1">
+        <v>16.352237501405199</v>
+      </c>
+      <c r="C293" s="1">
+        <v>0.26409583467590397</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A294" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B294" s="1">
+        <v>16.311710862235199</v>
+      </c>
+      <c r="C294" s="1">
+        <v>0.26424448419416702</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A295" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B295" s="1">
+        <v>16.368589028451201</v>
+      </c>
+      <c r="C295" s="1">
+        <v>0.26363414452799</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A296" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B296" s="1">
+        <v>16.289962255694199</v>
+      </c>
+      <c r="C296" s="1">
+        <v>0.26464837628465498</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A297" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B297" s="1">
+        <v>16.347944436289598</v>
+      </c>
+      <c r="C297" s="1">
+        <v>0.27030866825799199</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18488,13 +21967,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D318508-EB39-4B19-9441-3235666F09D0}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -18539,7 +22018,7 @@
         <v>1.2279085192200808E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -18584,7 +22063,7 @@
         <v>0.70533132928470998</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -18619,7 +22098,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -18654,7 +22133,7 @@
         <v>0.17086804073973499</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -18689,7 +22168,7 @@
         <v>0.171697248433512</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -18724,7 +22203,7 @@
         <v>0.17443666559002999</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -18759,7 +22238,7 @@
         <v>0.17690051952166999</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -18794,7 +22273,7 @@
         <v>0.17654554655181801</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -18823,7 +22302,7 @@
         <v>0.17411860264206899</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -18852,7 +22331,7 @@
         <v>0.175935205113702</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -18881,7 +22360,7 @@
         <v>0.17427622300988699</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -18910,7 +22389,7 @@
         <v>0.17224969239811899</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -18939,7 +22418,7 @@
         <v>0.17435257559575301</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -18968,7 +22447,7 @@
         <v>0.171222354567128</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -18997,7 +22476,7 @@
         <v>0.17230494746765301</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -19026,7 +22505,7 @@
         <v>0.17976030708667101</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -19055,7 +22534,7 @@
         <v>0.174433801903358</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -19084,7 +22563,7 @@
         <v>0.17714435708530099</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -19110,7 +22589,7 @@
         <v>0.17371638201273101</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -19133,7 +22612,7 @@
         <v>0.17123203171632401</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -19156,7 +22635,7 @@
         <v>0.17318569822136001</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -19179,7 +22658,7 @@
         <v>0.17669669700448201</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -19199,7 +22678,7 @@
         <v>0.25295075090609098</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -19216,7 +22695,7 @@
         <v>0.256452611497334</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -19233,7 +22712,7 @@
         <v>0.25868777299010298</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -19250,7 +22729,7 @@
         <v>0.2539674766801</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -19264,7 +22743,7 @@
         <v>0.25848980394328103</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -19278,7 +22757,7 @@
         <v>0.25493042534243598</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -19292,7 +22771,7 @@
         <v>0.25702073078272197</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -19306,7 +22785,7 @@
         <v>0.25281370286486299</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -19320,7 +22799,7 @@
         <v>0.25787828139437702</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -19334,7 +22813,7 @@
         <v>0.255030114263046</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -19348,7 +22827,7 @@
         <v>0.25326708245889501</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -19362,7 +22841,7 @@
         <v>0.25901851572451601</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -19373,7 +22852,7 @@
         <v>0.22249606599096799</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -19381,7 +22860,7 @@
         <v>0.22770140189949001</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -19389,7 +22868,7 @@
         <v>0.22467693879523801</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -19397,7 +22876,7 @@
         <v>0.22590951148508701</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>
@@ -19415,12 +22894,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5AE877-64C3-4028-8147-765389663D58}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>246</v>
       </c>
@@ -19465,7 +22944,7 @@
         <v>5.1155359965755959E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -19510,7 +22989,7 @@
         <v>0.47681214118341592</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -19545,7 +23024,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -19580,7 +23059,7 @@
         <v>10.6539096425895</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -19615,7 +23094,7 @@
         <v>10.8579810008815</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -19650,7 +23129,7 @@
         <v>10.831312443746899</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -19685,7 +23164,7 @@
         <v>10.709515833036701</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -19720,7 +23199,7 @@
         <v>10.5903781690852</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>6</v>
       </c>
@@ -19749,7 +23228,7 @@
         <v>10.753363759575</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>7</v>
       </c>
@@ -19778,7 +23257,7 @@
         <v>10.653749196664901</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>8</v>
       </c>
@@ -19807,7 +23286,7 @@
         <v>10.8630753057798</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9</v>
       </c>
@@ -19836,7 +23315,7 @@
         <v>10.7208205400928</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
       </c>
@@ -19865,7 +23344,7 @@
         <v>10.6700806810118</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>11</v>
       </c>
@@ -19894,7 +23373,7 @@
         <v>10.6606574449491</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>12</v>
       </c>
@@ -19923,7 +23402,7 @@
         <v>10.8131728102025</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>13</v>
       </c>
@@ -19952,7 +23431,7 @@
         <v>10.8081420366551</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>14</v>
       </c>
@@ -19981,7 +23460,7 @@
         <v>10.586819027671799</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>15</v>
       </c>
@@ -20010,7 +23489,7 @@
         <v>10.7337029456849</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>16</v>
       </c>
@@ -20036,7 +23515,7 @@
         <v>10.7080767594852</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>17</v>
       </c>
@@ -20059,7 +23538,7 @@
         <v>10.6292015876151</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>18</v>
       </c>
@@ -20082,7 +23561,7 @@
         <v>10.6922490647235</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>19</v>
       </c>
@@ -20105,7 +23584,7 @@
         <v>10.661460418557301</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>20</v>
       </c>
@@ -20125,7 +23604,7 @@
         <v>15.924948044130501</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>21</v>
       </c>
@@ -20142,7 +23621,7 @@
         <v>15.963192712237699</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>22</v>
       </c>
@@ -20159,7 +23638,7 @@
         <v>15.8676552218831</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -20176,7 +23655,7 @@
         <v>15.928435989248699</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -20190,7 +23669,7 @@
         <v>15.4712021433598</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -20204,7 +23683,7 @@
         <v>15.4267437621642</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -20218,7 +23697,7 @@
         <v>15.363023447442201</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -20232,7 +23711,7 @@
         <v>15.4784018893041</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -20246,7 +23725,7 @@
         <v>15.598700910453401</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -20260,7 +23739,7 @@
         <v>15.699463941581101</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -20274,7 +23753,7 @@
         <v>15.751226314712399</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -20288,7 +23767,7 @@
         <v>15.601321813860199</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -20299,7 +23778,7 @@
         <v>13.9597270287277</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -20307,7 +23786,7 @@
         <v>13.946102058433601</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -20315,7 +23794,7 @@
         <v>13.9823014618208</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -20323,7 +23802,7 @@
         <v>13.749906400784599</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>36</v>
       </c>

--- a/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
+++ b/BeatnotePostHotCell/AllFitsF1=3_playing with.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CB86C3-BC88-4521-946B-C38277BB1D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276BDF60-ADE8-4023-A979-AE706728F51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Together" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="346">
   <si>
     <t>Date</t>
   </si>
@@ -1002,6 +1002,81 @@
   </si>
   <si>
     <t>Jun29,2026+6-02-58PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+10-01-11AM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+11-04-27AM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+12-29-37PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+12-50-34PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+12-58-35PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+1-42-43PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+2-04-26PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+2-13-49PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+2-44-43PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+2-53-14PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-01-33PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-10-00PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-18-31PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-37-15PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-50-02PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+3-58-54PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-08-15PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-16-19PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-25-35PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-33-28PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-42-00PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-49-59PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+4-59-09PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+5-07-22PM</t>
+  </si>
+  <si>
+    <t>Jul02,2026+9-53-21AM</t>
   </si>
 </sst>
 </file>
@@ -7131,6 +7206,245 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-5A79-43C7-A012-327EE2E82A5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>2-Jun</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'All Together'!$B$299:$B$329</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>14.824645793302301</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.4528707103913</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.6109532885724</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.525535608882601</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.703570164436799</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.6469605754983</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.4430203101595</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.549598435905899</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.7043335718615</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.770828981153199</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.7903674498711</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.6129136258226</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.5285253520751</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.4495865267067</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.524765784844201</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>14.764112552014099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14.7106184874969</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.749177714501</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14.6684970880551</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.5764121579489</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>14.633716179029699</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14.618198212113001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>14.482642723981799</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.491750683935599</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>14.610387851091801</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>16.418772327555299</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>16.352237501405199</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>16.311710862235199</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>16.368589028451201</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>16.289962255694199</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>16.347944436289598</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'All Together'!$C$299:$C$329</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="31"/>
+                <c:pt idx="0">
+                  <c:v>0.24180291421483799</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.23775144209915899</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.24065215342237201</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.238634580986853</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24123516367901099</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.23838761262462899</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23787175668006799</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.235957408677299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.23761103430247099</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.24049928819975</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.23875237313230799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.23577509684512599</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.23798590162913699</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.23776270729380899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.23525871098023601</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.23822698567085801</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.236137249858582</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.236589149526167</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.234995035195148</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.238435257488993</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.23631298859917599</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.238968925765909</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.237506075673066</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.237718713583811</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.23747635372092801</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.26184487099436499</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26409583467590397</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.26424448419416702</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.26363414452799</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.26464837628465498</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.27030866825799199</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-98E0-4FAF-A3DC-7EEEAA62D55C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -18121,15 +18435,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>853656</xdr:colOff>
-      <xdr:row>256</xdr:row>
-      <xdr:rowOff>503207</xdr:rowOff>
+      <xdr:colOff>485235</xdr:colOff>
+      <xdr:row>291</xdr:row>
+      <xdr:rowOff>143772</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>530165</xdr:colOff>
-      <xdr:row>268</xdr:row>
-      <xdr:rowOff>122804</xdr:rowOff>
+      <xdr:colOff>161744</xdr:colOff>
+      <xdr:row>303</xdr:row>
+      <xdr:rowOff>149760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18576,7 +18890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P298"/>
+  <dimension ref="A1:P329"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
@@ -21957,6 +22271,347 @@
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
+    </row>
+    <row r="299" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A299" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B299" s="1">
+        <v>14.824645793302301</v>
+      </c>
+      <c r="C299" s="1">
+        <v>0.24180291421483799</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B300" s="1">
+        <v>14.4528707103913</v>
+      </c>
+      <c r="C300" s="1">
+        <v>0.23775144209915899</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B301" s="1">
+        <v>14.6109532885724</v>
+      </c>
+      <c r="C301" s="1">
+        <v>0.24065215342237201</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A302" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B302" s="1">
+        <v>14.525535608882601</v>
+      </c>
+      <c r="C302" s="1">
+        <v>0.238634580986853</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B303" s="1">
+        <v>14.703570164436799</v>
+      </c>
+      <c r="C303" s="1">
+        <v>0.24123516367901099</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A304" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B304" s="1">
+        <v>14.6469605754983</v>
+      </c>
+      <c r="C304" s="1">
+        <v>0.23838761262462899</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A305" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B305" s="1">
+        <v>14.4430203101595</v>
+      </c>
+      <c r="C305" s="1">
+        <v>0.23787175668006799</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A306" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B306" s="1">
+        <v>14.549598435905899</v>
+      </c>
+      <c r="C306" s="1">
+        <v>0.235957408677299</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A307" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B307" s="1">
+        <v>14.7043335718615</v>
+      </c>
+      <c r="C307" s="1">
+        <v>0.23761103430247099</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A308" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B308" s="1">
+        <v>14.770828981153199</v>
+      </c>
+      <c r="C308" s="1">
+        <v>0.24049928819975</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B309" s="1">
+        <v>14.7903674498711</v>
+      </c>
+      <c r="C309" s="1">
+        <v>0.23875237313230799</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A310" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B310" s="1">
+        <v>14.6129136258226</v>
+      </c>
+      <c r="C310" s="1">
+        <v>0.23577509684512599</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A311" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B311" s="1">
+        <v>14.5285253520751</v>
+      </c>
+      <c r="C311" s="1">
+        <v>0.23798590162913699</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A312" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B312" s="1">
+        <v>14.4495865267067</v>
+      </c>
+      <c r="C312" s="1">
+        <v>0.23776270729380899</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A313" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B313" s="1">
+        <v>14.524765784844201</v>
+      </c>
+      <c r="C313" s="1">
+        <v>0.23525871098023601</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B314" s="1">
+        <v>14.764112552014099</v>
+      </c>
+      <c r="C314" s="1">
+        <v>0.23822698567085801</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B315" s="1">
+        <v>14.7106184874969</v>
+      </c>
+      <c r="C315" s="1">
+        <v>0.236137249858582</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A316" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B316" s="1">
+        <v>14.749177714501</v>
+      </c>
+      <c r="C316" s="1">
+        <v>0.236589149526167</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A317" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B317" s="1">
+        <v>14.6684970880551</v>
+      </c>
+      <c r="C317" s="1">
+        <v>0.234995035195148</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B318" s="1">
+        <v>14.5764121579489</v>
+      </c>
+      <c r="C318" s="1">
+        <v>0.238435257488993</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A319" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B319" s="1">
+        <v>14.633716179029699</v>
+      </c>
+      <c r="C319" s="1">
+        <v>0.23631298859917599</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A320" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B320" s="1">
+        <v>14.618198212113001</v>
+      </c>
+      <c r="C320" s="1">
+        <v>0.238968925765909</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A321" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B321" s="1">
+        <v>14.482642723981799</v>
+      </c>
+      <c r="C321" s="1">
+        <v>0.237506075673066</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A322" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B322" s="1">
+        <v>14.491750683935599</v>
+      </c>
+      <c r="C322" s="1">
+        <v>0.237718713583811</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B323" s="1">
+        <v>14.610387851091801</v>
+      </c>
+      <c r="C323" s="1">
+        <v>0.23747635372092801</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A324" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B324" s="1">
+        <v>16.418772327555299</v>
+      </c>
+      <c r="C324" s="1">
+        <v>0.26184487099436499</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B325" s="1">
+        <v>16.352237501405199</v>
+      </c>
+      <c r="C325" s="1">
+        <v>0.26409583467590397</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A326" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B326" s="1">
+        <v>16.311710862235199</v>
+      </c>
+      <c r="C326" s="1">
+        <v>0.26424448419416702</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A327" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B327" s="1">
+        <v>16.368589028451201</v>
+      </c>
+      <c r="C327" s="1">
+        <v>0.26363414452799</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B328" s="1">
+        <v>16.289962255694199</v>
+      </c>
+      <c r="C328" s="1">
+        <v>0.26464837628465498</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A329" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B329" s="1">
+        <v>16.347944436289598</v>
+      </c>
+      <c r="C329" s="1">
+        <v>0.27030866825799199</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
